--- a/docs/Modello_inventario.xlsx
+++ b/docs/Modello_inventario.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -853,26 +853,64 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Gli iPhone non si importano</t>
+          <t>Valori ammessi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sono gestiti solo a mano dal programma e non compaiono ne' nelle</t>
+          <t>Tipo:  Laptop,  Tablet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>importazioni ne' nelle esportazioni. Se ne inserisci qui, vengono</t>
+          <t>Stato: Disponibile,  In attesa ritiro,  Guasto in attesa tecnico,  Da rebuildare,  Controllare</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t>Le tendine funzionano in Excel e in LibreOffice. Numbers non le</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>importa: in quel caso scrivi i valori qui sopra, sono gli stessi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Gli iPhone non si importano</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sono gestiti solo a mano dal programma e non compaiono ne' nelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>importazioni ne' nelle esportazioni. Se ne inserisci qui, vengono</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ignorati.</t>
         </is>

--- a/docs/Modello_inventario.xlsx
+++ b/docs/Modello_inventario.xlsx
@@ -460,12 +460,12 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -481,22 +481,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Modello</t>
+          <t>Stato</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Modello/Descrizione</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Numero di serie</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <dataValidation sqref="B2:B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tipo non valido" error="Scegli Laptop o Tablet." type="list">
       <formula1>"Laptop,Tablet"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stato non valido" error="Scegli uno degli stati previsti." type="list">
+    <dataValidation sqref="C2:C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stato non valido" error="Scegli uno degli stati previsti." type="list">
       <formula1>"Disponibile,In attesa ritiro,Guasto in attesa tecnico,Da rebuildare,Controllare"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Modello_inventario.xlsx
+++ b/docs/Modello_inventario.xlsx
@@ -462,8 +462,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
@@ -481,12 +481,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Stato</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -723,7 +723,7 @@
     <dataValidation sqref="B2:B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tipo non valido" error="Scegli Laptop o Tablet." type="list">
       <formula1>"Laptop,Tablet"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stato non valido" error="Scegli uno degli stati previsti." type="list">
+    <dataValidation sqref="D2:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stato non valido" error="Scegli uno degli stati previsti." type="list">
       <formula1>"Disponibile,In attesa ritiro,Guasto in attesa tecnico,Da rebuildare,Controllare"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Modello_inventario.xlsx
+++ b/docs/Modello_inventario.xlsx
@@ -457,15 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -481,22 +479,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Stanza</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Modello/Descrizione</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Numero di serie</t>
         </is>
       </c>
     </row>
@@ -512,64 +500,48 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -583,64 +555,48 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -654,77 +610,61 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B2:B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tipo non valido" error="Scegli Laptop o Tablet." type="list">
       <formula1>"Laptop,Tablet"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stato non valido" error="Scegli uno degli stati previsti." type="list">
-      <formula1>"Disponibile,In attesa ritiro,Guasto in attesa tecnico,Da rebuildare,Controllare"</formula1>
+    <dataValidation sqref="C2:C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Stanza non valida" error="Scegli una delle stanze configurate." type="list">
+      <formula1>"Site Services BAU,Digital Kiosk,Magazzino Disaster Recovery"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -737,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -794,123 +734,158 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- Asset Tag e Modello sono indispensabili; il numero di serie e'</t>
+          <t>- L'Asset Tag e' l'unico dato indispensabile: senza, la riga viene</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vivamente consigliato.</t>
+          <t xml:space="preserve">  scartata. Tipo, stanza e note si possono lasciare vuoti.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- L'asset tag identifica il dispositivo: importando due volte lo</t>
+          <t>- Il modello ha le stesse colonne di un file esportato: puoi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  stesso asset tag, la scheda viene aggiornata invece che duplicata.</t>
+          <t xml:space="preserve">  esportare, correggere in Excel e reimportare.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Tipo e Stato hanno la tendina: usa i valori proposti.</t>
+          <t>- Servono altre colonne? Aggiungile: modello, numero di serie e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Puoi aggiungere righe sotto un separatore, o spostare i separatori.</t>
+          <t xml:space="preserve">  stato vengono riconosciuti dal nome e importati lo stesso.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- Non cambiare i nomi delle colonne nella prima riga.</t>
+          <t>- L'asset tag identifica il dispositivo: importando due volte lo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- Le righe lasciate vuote vengono semplicemente ignorate.</t>
+          <t xml:space="preserve">  stesso asset tag, la scheda viene aggiornata invece che duplicata.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- Tipo e Stanza hanno la tendina: usa i valori proposti.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Valori ammessi</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- La stanza si puo' anche non scriverla: la dicono i separatori.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tipo:  Laptop,  Tablet</t>
+          <t>- Puoi aggiungere righe sotto un separatore, o spostare i separatori.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stato: Disponibile,  In attesa ritiro,  Guasto in attesa tecnico,  Da rebuildare,  Controllare</t>
+          <t>- Non cambiare i nomi delle colonne nella prima riga.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Le tendine funzionano in Excel e in LibreOffice. Numbers non le</t>
+          <t>- Le righe lasciate vuote vengono semplicemente ignorate.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>importa: in quel caso scrivi i valori qui sopra, sono gli stessi.</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Valori ammessi</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Gli iPhone non si importano</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tipo:  Laptop,  Tablet</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sono gestiti solo a mano dal programma e non compaiono ne' nelle</t>
+          <t>Stato: Disponibile,  In attesa ritiro,  Guasto in attesa tecnico,  Da rebuildare,  Controllare</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>importazioni ne' nelle esportazioni. Se ne inserisci qui, vengono</t>
+          <t>Le tendine funzionano in Excel e in LibreOffice. Numbers non le</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t>importa: in quel caso scrivi i valori qui sopra, sono gli stessi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Gli iPhone non si importano</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sono gestiti solo a mano dal programma e non compaiono ne' nelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>importazioni ne' nelle esportazioni. Se ne inserisci qui, vengono</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ignorati.</t>
         </is>

--- a/docs/Modello_inventario.xlsx
+++ b/docs/Modello_inventario.xlsx
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -802,90 +802,149 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>- Puoi aggiungere righe sotto un separatore, o spostare i separatori.</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Non cambiare i nomi delle colonne nella prima riga.</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Copia e incolla</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>- Le righe lasciate vuote vengono semplicemente ignorate.</t>
+          <t>- Da qui puoi copiare intere colonne e incollarle nel programma:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  in Elimina + si incollano gli asset tag, uno per riga.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Valori ammessi</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>- Nel programma tutti i campi accettano Ctrl+C e Ctrl+V, e il</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tipo:  Laptop,  Tablet</t>
+          <t xml:space="preserve">  tasto destro apre Copia / Incolla.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stato: Disponibile,  In attesa ritiro,  Guasto in attesa tecnico,  Da rebuildare,  Controllare</t>
+          <t>- Dall'elenco del programma si copia la riga selezionata con</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Le tendine funzionano in Excel e in LibreOffice. Numbers non le</t>
+          <t xml:space="preserve">  Ctrl+C, o l'identificativo da solo con il tasto destro: si</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>importa: in quel caso scrivi i valori qui sopra, sono gli stessi.</t>
+          <t xml:space="preserve">  incolla qui dentro cosi' com'e'.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Puoi aggiungere righe sotto un separatore, o spostare i separatori.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Gli iPhone non si importano</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Non cambiare i nomi delle colonne nella prima riga.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>- Le righe lasciate vuote vengono semplicemente ignorate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Valori ammessi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tipo:  Laptop,  Tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stato: Disponibile,  In attesa ritiro,  Guasto in attesa tecnico,  Da rebuildare,  Controllare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Le tendine funzionano in Excel e in LibreOffice. Numbers non le</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>importa: in quel caso scrivi i valori qui sopra, sono gli stessi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Gli iPhone non si importano</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Sono gestiti solo a mano dal programma e non compaiono ne' nelle</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>importazioni ne' nelle esportazioni. Se ne inserisci qui, vengono</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>ignorati.</t>
         </is>
